--- a/RESULTS/2021/CLASS/SS3/English_language/results.xlsx
+++ b/RESULTS/2021/CLASS/SS3/English_language/results.xlsx
@@ -413,102 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Yahaya Aisha Dangana</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>std338</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>SS3</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ENGLISH</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1" t="n">
-        <v>80</v>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2025-12-14 00:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Mohammad Usman</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>std345</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SS3</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ENGLISH</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>80</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2025-12-14 00:21</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>